--- a/光伏配储项目/电价数据/2026/望洋厂.xlsx
+++ b/光伏配储项目/电价数据/2026/望洋厂.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.55383</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.5201</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.8537899999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.1335</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.02037</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.91631</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.7064</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.7161000000000001</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44107</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.53335</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.58574</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.51889</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.6775599999999999</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.6778</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.6678200000000001</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.5122100000000001</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.6955399999999999</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.68572</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.6481699999999999</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.67401</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.52074</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.6885599999999999</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39492</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.5409700000000001</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.68659</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.69447</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.5452100000000001</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.71957</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.81025</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40257</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.86739</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.68263</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.6761</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.45874</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.7404700000000001</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.76371</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.39901</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.02355</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1.00848</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.09835</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.7504999999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.70768</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.5064</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.40667</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40415</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.40801</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.7829700000000001</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.96147</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.32241</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.5241699999999999</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.7673099999999999</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.44722</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.7764800000000001</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.75305</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.97265</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.90335</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.05659</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.3253</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.15856</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.17386</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.7379199999999999</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.22216</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.17544</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.09589</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.23472</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.53704</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.11189</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.26053</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.47897</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.31599</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.24426</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.42917</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.36118</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.29236</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.8071499999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47985</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.41025</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41277</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42198</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.17525</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.04571</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.17785</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53769</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52275</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5064</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51434</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.6089600000000001</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.5099900000000001</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.58321</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.4887</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.48124</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.51534</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.49774</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.5079</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.5079</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.49753</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.50441</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.55296</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.75988</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.06369</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.84221</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.58612</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.48148</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.53562</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.45315</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.50457</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.94253</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.15617</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.78016</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.12351</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.04163</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.99251</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.71104</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.54649</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.56789</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.6809700000000001</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.17523</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.23415</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.48073</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.17436</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.6446</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.09203</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.83521</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.26437</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.14844</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.27584</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.6199600000000001</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.63417</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.56211</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.6145499999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.17652</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.17352</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.17234</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.17453</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.9839</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.19084</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.19112</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.18794</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.67411</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.19061</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.21671</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.24651</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.5455</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.45288</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.19014</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.51456</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.27498</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.74879</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7638200000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.92175</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33631</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.59663</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.67835</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.6859</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.52699</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.57213</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.50344</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.81879</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.58653</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.58753</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.55649</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.55131</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.62548</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.48344</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.57404</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.4834</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.57078</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.52019</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.55159</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.49038</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.50948</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.49289</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.50385</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.4612</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.8329</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.10647</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.89136</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.7570800000000001</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.72142</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.63476</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.6515599999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.43709</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.75615</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.17494</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.54033</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.18697</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.63459</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.18697</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.17108</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.8002400000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.94926</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.17327</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.17297</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.8938200000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5590900000000001</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47505</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.67314</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.17557</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.03448</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.17392</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.40711</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.2618</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.17429</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.22212</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.21144</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.41828</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.28152</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.64878</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.18701</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.18701</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.04928</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.08466</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.10577</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.09176</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.21399</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.17448</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.25751</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>1.00344</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.75862</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.7158600000000001</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.53276</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41223</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3432</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.12412</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.7446799999999999</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.73363</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.18823</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.69524</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.8635</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.5531200000000001</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.58786</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.18857</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.58573</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.51935</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.65979</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.57897</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.5339700000000001</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.5122100000000001</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.5053299999999999</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.40754</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.45619</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.40684</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.45976</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.50478</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.51707</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.56985</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.49053</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.49044</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.45518</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.48925</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.6785099999999999</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.9299500000000001</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.17315</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.17144</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.84335</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.55107</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.659</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.8945</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.8714500000000001</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.15127</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.41916</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.7666</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.96154</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.21314</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.69929</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.12657</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.52516</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.48833</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.66049</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.00496</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.11276</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.25137</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.17043</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.0709</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.99015</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.02502</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.98898</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.24857</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.43815</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.7918200000000001</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.34316</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.18778</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.18866</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.84648</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.07217</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.15933</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.12078</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.1519</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.25288</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.31666</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.15209</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.26765</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.18702</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.18701</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.18703</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.18704</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.17253</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.14847</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.17323</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.5200199999999999</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.72762</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32138</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.74313</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.48884</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.47312</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.50361</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.5183</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.39814</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.45235</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.42349</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.45288</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.7106399999999999</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.8417100000000001</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.6086</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.69555</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.8417100000000001</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.70065</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.54449</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.54449</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.53528</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.58809</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.46932</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.08424</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.27571</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.26743</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.5452899999999999</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.47623</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46618</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.63215</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.5022099999999999</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.48262</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.39976</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.48784</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.48898</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40472</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.50727</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.50774</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.41092</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.4865</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40382</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34386</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.18474</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.96411</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.9799600000000001</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.58968</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.6432100000000001</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.5388999999999999</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.52386</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.53816</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.50628</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.50525</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.67444</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.52124</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.52166</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.50431</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.50505</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.26817</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07327</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04715</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04876</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.03845000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.07703</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.28443</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.12163</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.0044</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.24641</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.26969</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.27468</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.27801</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.44813</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.58799</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.53296</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.38468</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.38943</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.5550700000000001</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.5341900000000001</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.5335800000000001</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39479</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33388</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.55211</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.45329</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.26788</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30616</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30245</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.30695</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30194</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.28175</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.27783</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.28766</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26559</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.7425900000000001</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.8750599999999999</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.6799299999999999</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.6798200000000001</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.6895399999999999</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.74971</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.95233</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.42288</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.49226</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.74046</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.73098</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.8946900000000001</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.6292000000000001</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.5340199999999999</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48234</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.44851</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.08489000000000001</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.30184</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.73546</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.72623</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.63288</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.5997400000000001</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.7278300000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.78852</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.7822100000000001</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.59976</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.74097</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.01729</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.40465</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.84202</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.4336</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.29865</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.79118</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.38296</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.04447</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.40128</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.76786</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.44534</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.7775</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80364</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7876299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88051</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50503</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41496</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46342</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22207</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6430800000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54196</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.61229</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.5787899999999999</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.55862</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.56763</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.57387</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.5038</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.5752999999999999</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.55476</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.4647</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.48832</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.47554</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.5356300000000001</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.5063500000000001</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.5141699999999999</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.51107</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.50935</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.54452</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.51025</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.56111</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.46631</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.5628</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.48832</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.6001799999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43704</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59596</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5632999999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66864</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07962</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.64663</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.52263</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.56862</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59848</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.9569299999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.33533</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.30311</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.28331</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.56875</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.80159</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.57396</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.65038</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.98045</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.77961</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.72476</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.63447</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.57456</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.9790399999999999</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.92449</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.78394</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.53304</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.66127</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.5832999999999999</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.66565</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.61913</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.65971</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.69868</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.63739</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.6592100000000001</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.58162</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.57853</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.65626</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.67073</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.61718</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.66428</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.68545</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.75986</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.6751699999999999</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.75381</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.6846599999999999</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.6755800000000001</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.6795099999999999</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.66812</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.6577200000000001</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.61437</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.6564800000000001</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.59872</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.53632</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.60211</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.54972</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.57505</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.55122</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.53626</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.5257200000000001</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.46437</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95117</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.57113</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.59735</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.6158400000000001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.67089</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.5316000000000001</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.54331</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.49385</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.5182100000000001</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.48836</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.64051</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.40854</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.51185</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.61649</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.7257</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.86891</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.10925</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.9307799999999999</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.5442</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.1126</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.84223</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.9471000000000001</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.8576699999999999</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.63901</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.81123</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.06574</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.5673400000000001</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.52206</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37261</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.86886</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.5242</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.18607</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.78235</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.81191</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.73482</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.73851</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47495</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44311</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39753</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.49942</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43244</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41492</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44782</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59663</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.19584</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51021</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7027</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79415</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6489299999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58282</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43711</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.72215</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.42411</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.7382000000000001</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.15454</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.9101699999999999</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.64371</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.6527</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.69677</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.53879</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.57809</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.1003</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.59094</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.8907</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.57538</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.26154</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.24767</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.21442</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.21345</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.31301</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.80411</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.75138</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.51371</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.58101</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.8526699999999999</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.5044</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.74585</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.0539</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.07523</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.89723</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.9839</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.9358099999999999</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.17374</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.15442</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.86294</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.15574</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.60809</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.9707899999999999</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.01626</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.1551</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.9508300000000001</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.99107</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.55664</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.91625</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.98197</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.03771</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.88662</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.86581</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.66179</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.09728</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.55456</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.9609500000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.99181</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.7449600000000001</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33147</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.6010700000000001</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.48491</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.48788</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.50185</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.44156</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.56933</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.38603</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.57441</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.4851</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.46773</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.48322</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.47929</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.52232</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.41403</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.53638</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.5611900000000001</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.71012</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.8336</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.5612699999999999</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.5632699999999999</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.56301</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.50218</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.49059</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.54564</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.60277</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.53612</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.56121</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.4361</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.44994</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.45511</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.67643</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37772</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40235</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.5381900000000001</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.5059900000000001</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45647</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.5079</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.5011100000000001</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.50468</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34932</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.55492</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.44605</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46858</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.46613</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.56371</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.52171</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.52838</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.51537</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.54201</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.48658</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.50895</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.43641</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.43509</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.49524</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.51575</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.52191</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.5177999999999999</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.48004</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.46718</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.45031</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.5883999999999999</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.39022</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.48025</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.41088</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48664</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.69551</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.59741</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.62782</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.85225</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.27159</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16868</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.85222</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45067</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42996</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.70131</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.95248</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.13555</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.13301</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.55072</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43902</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42944</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39723</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44568</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42467</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.56329</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.4569</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.4547</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.4569</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.43428</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.49637</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.39901</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.43301</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.43736</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.47959</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.5017</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.50262</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.57529</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.7069500000000001</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.04388</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.10674</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.98985</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.97824</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.97915</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56514</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.55159</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.9455800000000001</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.1033</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.79887</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.02274</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.78623</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.65102</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.64102</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.72973</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.8119700000000001</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.0025</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.59418</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.7241799999999999</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.38664</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.21252</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.62602</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.65876</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67112</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.6662</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.64296</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.66602</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20694</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70115</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.78157</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.69752</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.70588</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.71329</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.6331</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.74757</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.02177</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.13149</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69224</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.69988</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.69426</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.77855</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.72341</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.8127300000000001</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.66575</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.46318</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.05918</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.46239</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.57498</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.45156</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.48435</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34345</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.44644</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.5959500000000001</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.1706</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.47192</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.49449</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39107</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.48362</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.50104</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.49418</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.4888</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.4491</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.43757</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39699</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40208</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42604</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.7465599999999999</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49492</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.51057</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.5189400000000001</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28461</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40659</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45211</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.9225099999999999</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.47587</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.17965</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.90234</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.7679400000000001</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39565</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45543</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50025</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.49728</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.44873</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.4882</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34924</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40462</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40488</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.43753</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.44792</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.74661</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42781</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.5149600000000001</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.68277</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49727</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.4059700000000001</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42691</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42315</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56649</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38958</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42499</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45359</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40068</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.44888</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.44491</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40107</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6411</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.81704</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.46783</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.39127</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.44708</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.345</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.51925</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.48386</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.47882</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.69029</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.46715</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.4379</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.42507</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.39668</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.40764</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.39559</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43911</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51678</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.4206</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.55316</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.76225</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.76801</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27746</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.47998</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.5465</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50152</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.7387699999999999</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.76267</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50164</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45068</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.02028</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.4869</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.4594</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.10767</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.13608</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.09529</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.39199</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.12411</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.14114</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.02993</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.20538</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.15326</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.14146</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.19543</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.85182</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.20104</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.85753</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.35555</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.9032899999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.7382</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.75479</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.64322</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.38517</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.53796</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.53783</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.5275299999999999</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.5305299999999999</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.46177</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36002</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.7563200000000001</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.39981</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.36141</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42775</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.51346</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.60789</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.60205</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.52598</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.50813</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.5699</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.5855399999999999</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.58609</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.51242</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.57969</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.5272100000000001</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.5689</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.5017</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.45888</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.46671</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.46671</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.49966</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.42864</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.49677</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45684</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.63476</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.54532</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.49699</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.6789400000000001</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.53561</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.78655</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.75115</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.27669</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.35099</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.72914</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.65448</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.35984</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.99307</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.58904</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.4971</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.49724</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.54789</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.59527</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.74481</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.18701</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.92874</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.6757300000000001</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.9502699999999999</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.89151</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.74328</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.71259</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.17329</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.17678</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.43288</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.25587</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.65601</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.24151</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.28603</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.42362</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.03635</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.66252</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.63549</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.43132</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.15406</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.63888</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.47382</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.50573</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45424</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42848</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40804</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44921</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48545</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.5307200000000001</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.68471</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50905</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.08743</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.69683</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66256</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.80001</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.0825</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.18701</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.49925</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.18701</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.54228</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.14792</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.55384</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.5658</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42041</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.4955</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.2325</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37303</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42939</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.4812</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.45035</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.5005299999999999</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.45115</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.45019</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.42011</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.52274</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.51789</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.60166</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.7555599999999999</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.12698</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.6833899999999999</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.54799</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.44485</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.40601</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.4164</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.41801</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.44521</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.39537</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.49178</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.45277</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.44738</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37939</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41787</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44849</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.59063</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.48161</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.46059</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39891</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46152</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.44816</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.45899</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.38718</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44843</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.41969</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39294</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.4079</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.45933</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.41892</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46762</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.48899</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.47313</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.47753</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.49528</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.45753</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.40438</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.36813</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3694</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.85715</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.39801</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.47946</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.40305</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.43853</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.43263</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.42753</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.42753</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23252</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.26578</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.29598</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.15016</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.72477</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.21053</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.38068</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.29598</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.26797</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.1372</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.68802</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.56589</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.28408</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.49131</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.48827</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36459</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.39823</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.39795</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.41188</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.40588</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39346</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39137</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39146</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.4268</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.80133</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38233</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46536</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.48367</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.09127</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.36339</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.83848</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.79687</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.52086</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.75219</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51131</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41471</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42664</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42347</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40551</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39169</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44054</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.55232</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42287</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.4403</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.5042099999999999</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.72684</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42168</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.56641</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.7979400000000001</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45174</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40093</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.7525499999999999</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.40768</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52171</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.27674</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.28114</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.23305</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.07743</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.9725199999999999</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.29991</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.62598</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.54452</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38439</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49029</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.5742699999999999</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.74858</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.54555</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.5418999999999999</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.3954</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.22231</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.7478899999999999</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.74909</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.44608</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.49128</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.9977699999999999</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.7602599999999999</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.61754</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.74909</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.18625</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.60026</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.74327</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.63405</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.25229</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.89209</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.87713</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.89723</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.91535</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.16333</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.64597</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.94973</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.6888300000000001</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.97548</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.63818</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.65804</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.75124</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.63818</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.25054</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.03477</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.01578</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.02467</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.5295</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.34787</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.04637</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.40959</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.75375</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.38938</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34518</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.55603</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.80163</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.54661</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.7516499999999999</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.75391</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.55813</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.46828</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.45782</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42749</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.41876</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.41852</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42514</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.6255700000000001</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.58993</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.55384</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.5372400000000001</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.4475</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.47261</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.49396</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.5569400000000001</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.81467</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.17836</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.14321</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.05421</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.15569</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.7483</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.73725</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.06262</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.0866</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.68563</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.5559400000000001</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.56252</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.5624600000000001</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.47696</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.48093</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.54612</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.55091</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.54013</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.65646</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.54074</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.04233</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.65243</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.5461900000000001</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.49669</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.49716</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.49741</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.57436</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.5545399999999999</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.55821</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49732</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.5113</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42207</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.49907</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.55804</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.65665</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.16262</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.06667</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.65727</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.5786</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.16015</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.86363</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.65698</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.1491</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.83196</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49746</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.5092300000000001</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49738</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.43929</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.5326799999999999</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39857</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34455</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.7007000000000001</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.57587</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.58235</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.71349</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.54477</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.45025</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.38291</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.39639</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38651</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.62534</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5825199999999999</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.41538</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.63774</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.02837</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.2588</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.92545</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.9762799999999999</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.02398</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.9668600000000001</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.93443</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.9649099999999999</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.9479</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.93255</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.9425</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.69043</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.03741</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.67399</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.03436</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.11894</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.10041</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.7210700000000001</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.9382200000000001</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.86033</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.92615</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.54165</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.72034</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.74444</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.76772</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.22548</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.09426</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.03185</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.41848</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.34223</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.02807</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.10618</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.9317300000000001</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.76552</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.76366</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.8221900000000001</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.7081000000000001</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.70023</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.56751</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40529</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.46029</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.68864</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.73612</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.69476</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.369</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.7559400000000001</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36423</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.70221</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46168</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.74115</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.51954</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.50514</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.43908</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.01353</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.91034</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.02407</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.9220700000000001</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.04207</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1.02107</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.01907</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.1754</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.08428</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.10161</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.46758</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.67579</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.61887</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.72758</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.72066</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02549</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.71429</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.76569</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.14829</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.24032</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.44453</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.21352</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.36859</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.9886699999999999</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.4089</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.36765</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.77752</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.67542</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.4402</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.44084</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.80868</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.76358</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.8022</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.55335</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3756</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26742</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.4218</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38743</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.75385</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43959</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.39895</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37303</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37252</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.49779</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.81143</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.31458</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.00466</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.92967</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.95666</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.03416</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.164</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.06274</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.87515</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.69208</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.21997</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.20674</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.2088</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.15519</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.86936</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.7039299999999999</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09631</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.10633</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.10669</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.13149</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10567</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.51867</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.2009</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.65808</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.58087</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15175</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.74466</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.67338</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.17857</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.87259</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.06248</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.05553</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.08542</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.03825</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.0695</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.11788</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.04979</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.06169</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.17661</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16289</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.21575</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.19826</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.29828</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.1702</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.16719</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.12059</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.10207</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.12749</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.17777</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.19472</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17791</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.11584</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.69131</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.6283500000000001</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.5765800000000001</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.55726</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44954</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3762</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.55461</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.31431</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.31402</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.06836</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.47941</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.52079</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.4407799999999999</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.43222</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.43076</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.4389</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.43361</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39271</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38498</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.43575</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.4367</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.43277</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.42503</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.43132</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.42621</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.41983</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.41625</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37182</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84826</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.4188</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.57777</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.7021900000000001</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.71765</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.66849</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.94833</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.7613099999999999</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.9614299999999999</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.17507</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.31122</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.45089</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.44008</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.46932</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.55139</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.26591</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.85104</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.61925</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.73305</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.70729</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.51289</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.85005</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.91734</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.22349</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.6419</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.7226</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.6166200000000001</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.74011</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.60307</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.18694</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.40826</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.17501</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.17571</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.09176</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.06581</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.18019</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.08587</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.1757</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.04419</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.06916</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.19376</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.08392</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.54295</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.80767</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.80374</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.56441</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.20081</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.8486900000000001</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.84868</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.55904</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.5542999999999999</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.56228</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51539</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.55362</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41935</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.5209600000000001</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.5009100000000001</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45954</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45953</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43862</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49537</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.50022</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.5481200000000001</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.5213</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.52115</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.5575800000000001</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17584</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.88328</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.4941</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.17159</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.50989</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.56972</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.84358</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.7945</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.59668</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.8526699999999999</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.49976</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.5224500000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.54274</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.17659</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.55635</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.17501</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.58168</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.55553</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.85025</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.6838099999999999</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.05244</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.17587</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.17619</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.17604</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.82397</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.73266</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.64586</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.67413</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.6814199999999999</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.72746</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.83087</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.81001</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.60181</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.7485000000000001</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.12965</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.7459</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.60133</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.62338</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.6285299999999999</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.60114</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.60099</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.6898500000000001</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.65061</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.69096</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.52091</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.5009100000000001</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37241</v>
       </c>
     </row>
   </sheetData>
